--- a/order_generation/PO_excel_export/test-1.xlsx
+++ b/order_generation/PO_excel_export/test-1.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>宁波市海曙硕丰塑料五金制品有限公司</t>
+          <t>宁波瑾秀制刷科技有限公司</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
@@ -811,7 +811,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>电话: +86-574-27889688   传真: +86-574-27889677</t>
+          <t>+86-574-27889688</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>2026年02月02日</t>
+          <t>2026年02月03日</t>
         </is>
       </c>
       <c r="H4" s="9" t="n"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>小张</t>
+          <t>多多</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>孙诚昱</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="H5" s="9" t="n"/>
@@ -899,26 +899,30 @@
     <row r="7" ht="100" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>ST1122-1</t>
+          <t>Elasticbrush01</t>
         </is>
       </c>
       <c r="B7" s="16" t="n"/>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>黑色气垫猪鬃手柄：水曲柳手柄棕黑色喷漆双层，喷漆效果参考Moroccooil，形状同寄样。8.5*24.5*1.3，金色移印logoNorsewood。梳面开口严格按照提供线稿，礼盒包装我司提供，胶皮配件我司提供，清洁刷和布袋我司提供，需装配，贴标。</t>
+          <t>梳身半降解材料（用新材料防断裂）加麦秸秆5645 C绿色（注意大货注塑颜色，必须与2025.5.30签样一样），尼龙丝0.8mm7529U灰色尼龙丝颜色同beter，棕色 ecoed logo颜色同beter！染头颜色同梳体. 包装方式：白卡盒，卡盒我司供，箱规120/24</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>2222</v>
+        <v>1200</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>8.800000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="F7" s="17">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="16" t="inlineStr"/>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>白卡盒，卡盒我司供，箱规120/24</t>
+        </is>
+      </c>
       <c r="H7" s="15" t="n"/>
       <c r="I7" s="34" t="n"/>
     </row>
@@ -984,7 +988,7 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>宁波市海曙区高桥镇秀丰路67号1栋1楼，小张，18668289261</t>
+          <t>浙江宁波市余姚市陆埠镇五马工业区创利西路15号</t>
         </is>
       </c>
       <c r="C12" s="21" t="n"/>
@@ -1003,7 +1007,7 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>含税含运含进仓</t>
+          <t>凭发票，出货45天付款，含税含运含进仓</t>
         </is>
       </c>
       <c r="C13" s="21" t="n"/>
@@ -1047,7 +1051,11 @@
           <t>箱规:</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr"/>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>箱规120/24</t>
+        </is>
+      </c>
       <c r="C15" s="21" t="n"/>
       <c r="D15" s="22" t="n"/>
       <c r="E15" s="21" t="n"/>
@@ -1104,12 +1112,7 @@
     <row r="19" ht="21.75" customHeight="1">
       <c r="A19" s="21" t="inlineStr">
         <is>
-          <t>双层漆效果参考以寄样为准，
-配件需要全部入纸袋然后放进礼盒包装，
-双层漆效果参考以寄样为准，
-木柄表面处理平整干净，没有坑洼， 气垫与木柄交接处，没有缝隙
-配件需要全部入纸袋然后放进礼盒包装，
-气垫梳60/箱 80箱</t>
+          <t>快速弯折120度，快速旋转120度不得断裂（20个样品最多一个）</t>
         </is>
       </c>
       <c r="B19" s="21" t="n"/>
@@ -1122,7 +1125,11 @@
       <c r="I19" s="34" t="n"/>
     </row>
     <row r="20" ht="21.75" customHeight="1">
-      <c r="A20" s="21" t="inlineStr"/>
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>注意柄部干净整洁，logo处清洁摸上去没有油</t>
+        </is>
+      </c>
       <c r="B20" s="21" t="n"/>
       <c r="C20" s="21" t="n"/>
       <c r="D20" s="22" t="n"/>
@@ -1133,7 +1140,11 @@
       <c r="I20" s="34" t="n"/>
     </row>
     <row r="21" ht="21.75" customHeight="1">
-      <c r="A21" s="21" t="inlineStr"/>
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>外箱单边不得超过60cm，重量不得超过20公斤</t>
+        </is>
+      </c>
       <c r="B21" s="21" t="n"/>
       <c r="C21" s="21" t="n"/>
       <c r="D21" s="22" t="n"/>
@@ -1144,7 +1155,11 @@
       <c r="I21" s="34" t="n"/>
     </row>
     <row r="22" ht="21.75" customHeight="1">
-      <c r="A22" s="21" t="inlineStr"/>
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>尼龙丝针注意不要大量明显弯曲</t>
+        </is>
+      </c>
       <c r="B22" s="21" t="n"/>
       <c r="C22" s="21" t="n"/>
       <c r="D22" s="22" t="n"/>
@@ -1155,7 +1170,11 @@
       <c r="I22" s="34" t="n"/>
     </row>
     <row r="23" ht="21.75" customHeight="1">
-      <c r="A23" s="21" t="inlineStr"/>
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>染头不能有坑(2个以上），（有坑一律次品）</t>
+        </is>
+      </c>
       <c r="B23" s="21" t="n"/>
       <c r="C23" s="21" t="n"/>
       <c r="D23" s="22" t="n"/>
@@ -1166,7 +1185,11 @@
       <c r="I23" s="34" t="n"/>
     </row>
     <row r="24" ht="21.75" customHeight="1">
-      <c r="A24" s="21" t="inlineStr"/>
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>染头不得粘连</t>
+        </is>
+      </c>
       <c r="B24" s="21" t="n"/>
       <c r="C24" s="21" t="n"/>
       <c r="D24" s="22" t="n"/>
@@ -1177,7 +1200,11 @@
       <c r="I24" s="23" t="n"/>
     </row>
     <row r="25" ht="21.75" customHeight="1">
-      <c r="A25" s="21" t="inlineStr"/>
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>每个外箱需要贴2个标签FBA标签一个，货代标签一个</t>
+        </is>
+      </c>
       <c r="B25" s="21" t="n"/>
       <c r="C25" s="21" t="n"/>
       <c r="D25" s="22" t="n"/>
@@ -1675,7 +1702,7 @@
       <c r="D69" s="30" t="n"/>
       <c r="E69" s="29" t="inlineStr">
         <is>
-          <t>宁波市海曙硕丰塑料五金制品有限公司</t>
+          <t>宁波瑾秀制刷科技有限公司</t>
         </is>
       </c>
       <c r="F69" s="31" t="n"/>
